--- a/Team-Data/2008-09/1-27-2008-09.xlsx
+++ b/Team-Data/2008-09/1-27-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>10</v>
@@ -769,31 +836,31 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
         <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -843,22 +910,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8</v>
+        <v>0.804</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J3" t="n">
         <v>77</v>
@@ -873,28 +940,28 @@
         <v>17.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.388</v>
+        <v>0.385</v>
       </c>
       <c r="O3" t="n">
         <v>20.3</v>
       </c>
       <c r="P3" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.773</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T3" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U3" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V3" t="n">
         <v>15.9</v>
@@ -903,40 +970,40 @@
         <v>8.5</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.4</v>
+        <v>101.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
@@ -948,7 +1015,7 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN3" t="n">
         <v>4</v>
@@ -960,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
@@ -969,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
@@ -978,22 +1045,22 @@
         <v>28</v>
       </c>
       <c r="AW3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA3" t="n">
         <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -1025,34 +1092,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>0.422</v>
+        <v>0.409</v>
       </c>
       <c r="H4" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="J4" t="n">
-        <v>76.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M4" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="N4" t="n">
         <v>0.354</v>
@@ -1061,22 +1128,22 @@
         <v>18.5</v>
       </c>
       <c r="P4" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.744</v>
+        <v>0.746</v>
       </c>
       <c r="R4" t="n">
         <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>29</v>
+        <v>28.7</v>
       </c>
       <c r="T4" t="n">
-        <v>39.6</v>
+        <v>39.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="V4" t="n">
         <v>15.4</v>
@@ -1094,28 +1161,28 @@
         <v>22.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF4" t="n">
         <v>19</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>20</v>
       </c>
       <c r="AG4" t="n">
         <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,10 +1191,10 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
         <v>25</v>
@@ -1136,7 +1203,7 @@
         <v>20</v>
       </c>
       <c r="AO4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
         <v>17</v>
@@ -1145,25 +1212,25 @@
         <v>25</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
         <v>24</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1172,7 +1239,7 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0.386</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J5" t="n">
-        <v>84.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L5" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N5" t="n">
         <v>0.374</v>
       </c>
       <c r="O5" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="P5" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.794</v>
+        <v>0.792</v>
       </c>
       <c r="R5" t="n">
         <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
         <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V5" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W5" t="n">
         <v>7.3</v>
@@ -1270,37 +1337,37 @@
         <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.09999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.8</v>
+        <v>-3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF5" t="n">
         <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
         <v>4</v>
@@ -1318,10 +1385,10 @@
         <v>11</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1333,31 +1400,31 @@
         <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
         <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
         <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
         <v>24</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -1392,124 +1459,124 @@
         <v>42</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.833</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.3</v>
+        <v>78</v>
       </c>
       <c r="K6" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="M6" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.372</v>
+        <v>0.368</v>
       </c>
       <c r="O6" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.754</v>
+        <v>0.751</v>
       </c>
       <c r="R6" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="S6" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U6" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.9</v>
       </c>
       <c r="X6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.6</v>
+        <v>100.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="AD6" t="n">
         <v>29</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM6" t="n">
         <v>5</v>
       </c>
-      <c r="AM6" t="n">
-        <v>4</v>
-      </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1518,28 +1585,28 @@
         <v>14</v>
       </c>
       <c r="AU6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY6" t="n">
         <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>0.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1679,7 +1746,7 @@
         <v>7</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -1753,46 +1820,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" t="n">
         <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>0.667</v>
+        <v>0.659</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J8" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="L8" t="n">
         <v>6.8</v>
       </c>
       <c r="M8" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="N8" t="n">
         <v>0.375</v>
       </c>
       <c r="O8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="P8" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
@@ -1804,34 +1871,34 @@
         <v>41.2</v>
       </c>
       <c r="U8" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="W8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Y8" t="n">
         <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.5</v>
+        <v>104.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1843,13 +1910,13 @@
         <v>6</v>
       </c>
       <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>22</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>23</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1858,7 +1925,7 @@
         <v>14</v>
       </c>
       <c r="AM8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN8" t="n">
         <v>10</v>
@@ -1882,16 +1949,16 @@
         <v>18</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY8" t="n">
         <v>27</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
         <v>14</v>
@@ -2028,7 +2095,7 @@
         <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
@@ -2055,7 +2122,7 @@
         <v>27</v>
       </c>
       <c r="AR9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS9" t="n">
         <v>17</v>
@@ -2064,7 +2131,7 @@
         <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2082,7 +2149,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
         <v>27</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>25</v>
@@ -2210,7 +2277,7 @@
         <v>7</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
         <v>2</v>
@@ -2222,7 +2289,7 @@
         <v>17</v>
       </c>
       <c r="AM10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN10" t="n">
         <v>17</v>
@@ -2234,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR10" t="n">
         <v>5</v>
@@ -2246,10 +2313,10 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2261,7 +2328,7 @@
         <v>25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2465,7 @@
         <v>17</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2407,7 +2474,7 @@
         <v>9</v>
       </c>
       <c r="AN11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO11" t="n">
         <v>10</v>
@@ -2425,7 +2492,7 @@
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
         <v>22</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -2481,55 +2548,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
         <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>0.378</v>
+        <v>0.386</v>
       </c>
       <c r="H12" t="n">
         <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J12" t="n">
         <v>86.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="L12" t="n">
         <v>7.4</v>
       </c>
       <c r="M12" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N12" t="n">
         <v>0.363</v>
       </c>
       <c r="O12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q12" t="n">
         <v>0.8090000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="S12" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.5</v>
+        <v>43.9</v>
       </c>
       <c r="U12" t="n">
         <v>22.9</v>
@@ -2538,7 +2605,7 @@
         <v>15.2</v>
       </c>
       <c r="W12" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X12" t="n">
         <v>5</v>
@@ -2550,31 +2617,31 @@
         <v>23.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.3</v>
+        <v>104.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.6</v>
+        <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
         <v>23</v>
       </c>
       <c r="AH12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
         <v>1</v>
@@ -2583,7 +2650,7 @@
         <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM12" t="n">
         <v>8</v>
@@ -2592,10 +2659,10 @@
         <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
         <v>4</v>
@@ -2610,13 +2677,13 @@
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
         <v>12</v>
@@ -2625,16 +2692,16 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-7.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2765,7 +2832,7 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM13" t="n">
         <v>20</v>
@@ -2777,7 +2844,7 @@
         <v>26</v>
       </c>
       <c r="AP13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ13" t="n">
         <v>24</v>
@@ -2786,7 +2853,7 @@
         <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT13" t="n">
         <v>15</v>
@@ -2798,13 +2865,13 @@
         <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -2848,52 +2915,52 @@
         <v>43</v>
       </c>
       <c r="E14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.791</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>48.2</v>
+        <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="J14" t="n">
-        <v>83.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
         <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.376</v>
+        <v>0.381</v>
       </c>
       <c r="O14" t="n">
         <v>21</v>
       </c>
       <c r="P14" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R14" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="U14" t="n">
         <v>23.4</v>
@@ -2902,49 +2969,49 @@
         <v>13.8</v>
       </c>
       <c r="W14" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
         <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.9</v>
+        <v>107.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,13 +3029,13 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
         <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2977,19 +3044,19 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -3027,52 +3094,52 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E15" t="n">
         <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>0.25</v>
+        <v>0.256</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J15" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L15" t="n">
         <v>4.4</v>
       </c>
       <c r="M15" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.327</v>
+        <v>0.325</v>
       </c>
       <c r="O15" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="P15" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.752</v>
+        <v>0.754</v>
       </c>
       <c r="R15" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S15" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="T15" t="n">
         <v>38.2</v>
@@ -3081,31 +3148,31 @@
         <v>16.5</v>
       </c>
       <c r="V15" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="W15" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
         <v>4.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>92.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.8</v>
+        <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
@@ -3126,25 +3193,25 @@
         <v>28</v>
       </c>
       <c r="AK15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="n">
         <v>28</v>
       </c>
       <c r="AM15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN15" t="n">
         <v>29</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP15" t="n">
         <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
@@ -3162,16 +3229,16 @@
         <v>17</v>
       </c>
       <c r="AW15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX15" t="n">
         <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3308,7 +3375,7 @@
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
         <v>13</v>
@@ -3332,7 +3399,7 @@
         <v>22</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT16" t="n">
         <v>24</v>
@@ -3353,7 +3420,7 @@
         <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
         <v>26</v>
@@ -3362,7 +3429,7 @@
         <v>23</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" t="n">
         <v>22</v>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>0.468</v>
+        <v>0.458</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,10 +3476,10 @@
         <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L17" t="n">
         <v>5.6</v>
@@ -3421,34 +3488,34 @@
         <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.348</v>
+        <v>0.35</v>
       </c>
       <c r="O17" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P17" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R17" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="U17" t="n">
         <v>21.3</v>
       </c>
       <c r="V17" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X17" t="n">
         <v>3.7</v>
@@ -3457,16 +3524,16 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,7 +3542,7 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>9</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
         <v>22</v>
@@ -3499,13 +3566,13 @@
         <v>23</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
         <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ17" t="n">
         <v>9</v>
@@ -3514,7 +3581,7 @@
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT17" t="n">
         <v>13</v>
@@ -3526,16 +3593,16 @@
         <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX17" t="n">
         <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
         <v>6</v>
@@ -3544,7 +3611,7 @@
         <v>18</v>
       </c>
       <c r="BC17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-3</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
@@ -3663,13 +3730,13 @@
         <v>24</v>
       </c>
       <c r="AH18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI18" t="n">
         <v>13</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3702,7 +3769,7 @@
         <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
         <v>15</v>
@@ -3717,13 +3784,13 @@
         <v>30</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA18" t="n">
         <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-3</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3845,7 +3912,7 @@
         <v>18</v>
       </c>
       <c r="AH19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
@@ -3857,7 +3924,7 @@
         <v>27</v>
       </c>
       <c r="AL19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM19" t="n">
         <v>6</v>
@@ -3869,7 +3936,7 @@
         <v>8</v>
       </c>
       <c r="AP19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ19" t="n">
         <v>10</v>
@@ -3890,7 +3957,7 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX19" t="n">
         <v>21</v>
@@ -3902,7 +3969,7 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB19" t="n">
         <v>17</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -4036,10 +4103,10 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM20" t="n">
         <v>10</v>
@@ -4060,7 +4127,7 @@
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
         <v>19</v>
@@ -4245,7 +4312,7 @@
         <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
         <v>9</v>
@@ -4254,7 +4321,7 @@
         <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>19</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4272,7 +4339,7 @@
         <v>6</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-6.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4394,13 +4461,13 @@
         <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,7 +4476,7 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO22" t="n">
         <v>9</v>
@@ -4427,7 +4494,7 @@
         <v>11</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AU22" t="n">
         <v>24</v>
@@ -4439,13 +4506,13 @@
         <v>23</v>
       </c>
       <c r="AX22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY22" t="n">
         <v>23</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA22" t="n">
         <v>20</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -4483,61 +4550,61 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>0.773</v>
+        <v>0.767</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J23" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.462</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="M23" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.402</v>
+        <v>0.4</v>
       </c>
       <c r="O23" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="P23" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.723</v>
+        <v>0.72</v>
       </c>
       <c r="R23" t="n">
         <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="T23" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U23" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="V23" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W23" t="n">
         <v>7.2</v>
@@ -4555,16 +4622,16 @@
         <v>22.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.4</v>
+        <v>101.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="n">
         <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4594,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="AO23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP23" t="n">
         <v>6</v>
@@ -4609,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU23" t="n">
         <v>28</v>
@@ -4624,7 +4691,7 @@
         <v>6</v>
       </c>
       <c r="AY23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ23" t="n">
         <v>9</v>
@@ -4633,7 +4700,7 @@
         <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="n">
         <v>17</v>
@@ -4755,16 +4822,16 @@
         <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ24" t="n">
         <v>15</v>
       </c>
       <c r="AK24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4794,13 +4861,13 @@
         <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AV24" t="n">
         <v>25</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX24" t="n">
         <v>9</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
@@ -4952,7 +5019,7 @@
         <v>16</v>
       </c>
       <c r="AM25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN25" t="n">
         <v>5</v>
@@ -4970,13 +5037,13 @@
         <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
         <v>30</v>
@@ -4988,7 +5055,7 @@
         <v>13</v>
       </c>
       <c r="AY25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -5029,58 +5096,58 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E26" t="n">
         <v>27</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.628</v>
+        <v>0.614</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="J26" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M26" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="P26" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="T26" t="n">
         <v>40.8</v>
       </c>
       <c r="U26" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V26" t="n">
         <v>12.7</v>
@@ -5089,25 +5156,25 @@
         <v>7</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
@@ -5119,19 +5186,19 @@
         <v>8</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM26" t="n">
         <v>11</v>
@@ -5140,13 +5207,13 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,31 +5225,31 @@
         <v>20</v>
       </c>
       <c r="AU26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>0.217</v>
+        <v>0.222</v>
       </c>
       <c r="H27" t="n">
         <v>48.7</v>
@@ -5229,49 +5296,49 @@
         <v>36.2</v>
       </c>
       <c r="J27" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L27" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="M27" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="N27" t="n">
-        <v>0.351</v>
+        <v>0.347</v>
       </c>
       <c r="O27" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P27" t="n">
         <v>25.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.804</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S27" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="T27" t="n">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="U27" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V27" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W27" t="n">
         <v>6.7</v>
       </c>
       <c r="X27" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
         <v>5.2</v>
@@ -5283,49 +5350,49 @@
         <v>21.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="AC27" t="n">
         <v>-8.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
         <v>18</v>
       </c>
       <c r="AM27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>7</v>
       </c>
       <c r="AP27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
@@ -5334,16 +5401,16 @@
         <v>24</v>
       </c>
       <c r="AS27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT27" t="n">
         <v>27</v>
       </c>
-      <c r="AT27" t="n">
-        <v>28</v>
-      </c>
       <c r="AU27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW27" t="n">
         <v>24</v>
@@ -5358,10 +5425,10 @@
         <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,37 +5478,37 @@
         <v>36.7</v>
       </c>
       <c r="J28" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L28" t="n">
         <v>8.1</v>
       </c>
       <c r="M28" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.394</v>
+        <v>0.391</v>
       </c>
       <c r="O28" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="P28" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.759</v>
+        <v>0.763</v>
       </c>
       <c r="R28" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T28" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U28" t="n">
         <v>21.8</v>
@@ -5450,28 +5517,28 @@
         <v>12.1</v>
       </c>
       <c r="W28" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X28" t="n">
         <v>4.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z28" t="n">
         <v>18.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC28" t="n">
         <v>2.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5483,7 +5550,7 @@
         <v>5</v>
       </c>
       <c r="AH28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI28" t="n">
         <v>14</v>
@@ -5498,7 +5565,7 @@
         <v>3</v>
       </c>
       <c r="AM28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN28" t="n">
         <v>3</v>
@@ -5510,16 +5577,16 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5534,7 +5601,7 @@
         <v>22</v>
       </c>
       <c r="AY28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -5656,25 +5723,25 @@
         <v>2</v>
       </c>
       <c r="AE29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH29" t="n">
         <v>17</v>
       </c>
       <c r="AI29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>19</v>
@@ -5683,13 +5750,13 @@
         <v>22</v>
       </c>
       <c r="AN29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5701,7 +5768,7 @@
         <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>8</v>
@@ -5713,7 +5780,7 @@
         <v>26</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5722,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB29" t="n">
         <v>20</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
         <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>0.543</v>
+        <v>0.556</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
@@ -5781,7 +5848,7 @@
         <v>0.473</v>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="M30" t="n">
         <v>13.5</v>
@@ -5793,31 +5860,31 @@
         <v>21.3</v>
       </c>
       <c r="P30" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="R30" t="n">
         <v>12.1</v>
       </c>
       <c r="S30" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T30" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U30" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="V30" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W30" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
@@ -5826,16 +5893,16 @@
         <v>22.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB30" t="n">
         <v>101.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>11</v>
@@ -5847,7 +5914,7 @@
         <v>15</v>
       </c>
       <c r="AH30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI30" t="n">
         <v>5</v>
@@ -5862,10 +5929,10 @@
         <v>27</v>
       </c>
       <c r="AM30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,13 +5941,13 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT30" t="n">
         <v>16</v>
@@ -5889,13 +5956,13 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY30" t="n">
         <v>16</v>
@@ -5907,7 +5974,7 @@
         <v>3</v>
       </c>
       <c r="BB30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
@@ -6038,7 +6105,7 @@
         <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6065,22 +6132,22 @@
         <v>29</v>
       </c>
       <c r="AT31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX31" t="n">
         <v>25</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ31" t="n">
         <v>11</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-27-2008-09</t>
+          <t>2009-01-27</t>
         </is>
       </c>
     </row>
